--- a/poker/resources/sample/PointsAwardRanking.xlsx
+++ b/poker/resources/sample/PointsAwardRanking.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardRanking" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="58">
   <si>
     <t>序列ID</t>
   </si>
@@ -240,25 +240,28 @@
     <t>time</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1990000_27000000</t>
+  </si>
+  <si>
+    <t>test001.jpg</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
+    <t>test002.jpg</t>
+  </si>
+  <si>
+    <t>1990000_3000000</t>
+  </si>
+  <si>
+    <t>test003.jpg</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1990000_27000000</t>
-  </si>
-  <si>
-    <t>jfdj_box_1.png</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>jfdj_box_2.png</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>jfdj_box_3.png</t>
   </si>
   <si>
     <t>1990000_1000000</t>
@@ -1633,10 +1636,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
@@ -1655,10 +1658,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
@@ -1678,10 +1681,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
@@ -1701,10 +1704,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
@@ -1724,10 +1727,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
@@ -1747,10 +1750,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
@@ -1769,10 +1772,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -1788,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
@@ -1811,13 +1814,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -1834,13 +1837,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>34</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>33</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
@@ -1857,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
@@ -1880,13 +1883,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
@@ -1903,13 +1906,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>38</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>37</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
@@ -1926,13 +1929,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
@@ -1949,13 +1952,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
@@ -1972,13 +1975,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>43</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
@@ -1995,13 +1998,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
@@ -2018,13 +2021,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
@@ -2047,7 +2050,7 @@
         <v>21</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="16" t="s">
@@ -2072,7 +2075,7 @@
         <v>21</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="16" t="s">
@@ -2097,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="16" t="s">
@@ -2119,10 +2122,10 @@
         <v>4</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
@@ -2142,10 +2145,10 @@
         <v>5</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
@@ -2164,10 +2167,10 @@
         <v>6</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
@@ -2186,10 +2189,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
@@ -2208,10 +2211,10 @@
         <v>8</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
@@ -2230,10 +2233,10 @@
         <v>9</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
@@ -2252,10 +2255,10 @@
         <v>10</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
@@ -2272,13 +2275,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
@@ -2295,13 +2298,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>32</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>31</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -2318,13 +2321,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
@@ -2339,13 +2342,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
@@ -2360,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F40" s="16"/>
       <c r="G40" s="16"/>
@@ -2381,13 +2384,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
@@ -2408,7 +2411,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F42" s="16"/>
       <c r="G42" s="16" t="s">
@@ -2431,7 +2434,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F43" s="16"/>
       <c r="G43" s="16" t="s">
@@ -2454,7 +2457,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F44" s="16"/>
       <c r="G44" s="16" t="s">
@@ -2474,10 +2477,10 @@
         <v>4</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
@@ -2495,10 +2498,10 @@
         <v>5</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
@@ -2516,10 +2519,10 @@
         <v>6</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
@@ -2537,10 +2540,10 @@
         <v>7</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
@@ -2558,10 +2561,10 @@
         <v>8</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
@@ -2580,10 +2583,10 @@
         <v>9</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F50" s="16"/>
       <c r="G50" s="16"/>
@@ -2602,10 +2605,10 @@
         <v>10</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
@@ -2624,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E52" s="22" t="s">
         <v>22</v>
@@ -2634,7 +2637,7 @@
         <v>23</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
@@ -2650,7 +2653,7 @@
         <v>2</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>24</v>
@@ -2660,7 +2663,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I53" s="19"/>
       <c r="J53" s="19"/>
@@ -2676,7 +2679,7 @@
         <v>3</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E54" s="22" t="s">
         <v>26</v>
@@ -2686,7 +2689,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I54" s="19"/>
       <c r="J54" s="19"/>
@@ -2702,15 +2705,15 @@
         <v>4</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F55" s="22"/>
       <c r="G55" s="22"/>
       <c r="H55" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I55" s="19"/>
       <c r="J55" s="19"/>
@@ -2726,15 +2729,15 @@
         <v>5</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F56" s="22"/>
       <c r="G56" s="22"/>
       <c r="H56" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
@@ -2751,15 +2754,15 @@
         <v>6</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F57" s="22"/>
       <c r="G57" s="22"/>
       <c r="H57" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
@@ -2776,15 +2779,15 @@
         <v>7</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F58" s="22"/>
       <c r="G58" s="22"/>
       <c r="H58" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
@@ -2801,15 +2804,15 @@
         <v>8</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F59" s="22"/>
       <c r="G59" s="22"/>
       <c r="H59" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
@@ -2826,15 +2829,15 @@
         <v>9</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F60" s="22"/>
       <c r="G60" s="22"/>
       <c r="H60" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I60" s="19"/>
       <c r="L60" s="1"/>
@@ -2850,15 +2853,15 @@
         <v>10</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F61" s="22"/>
       <c r="G61" s="22"/>
       <c r="H61" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I61" s="19"/>
       <c r="L61" s="1"/>
@@ -2871,18 +2874,18 @@
         <v>1</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F62" s="22"/>
       <c r="G62" s="22"/>
       <c r="H62" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I62" s="19"/>
       <c r="J62" s="8"/>
@@ -2896,18 +2899,18 @@
         <v>1</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F63" s="22"/>
       <c r="G63" s="22"/>
       <c r="H63" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
@@ -2921,18 +2924,18 @@
         <v>1</v>
       </c>
       <c r="C64" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" s="22" t="s">
         <v>34</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>33</v>
       </c>
       <c r="F64" s="22"/>
       <c r="G64" s="22"/>
       <c r="H64" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
@@ -2946,18 +2949,18 @@
         <v>1</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F65" s="22"/>
       <c r="G65" s="22"/>
       <c r="H65" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
@@ -2971,18 +2974,18 @@
         <v>1</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F66" s="22"/>
       <c r="G66" s="22"/>
       <c r="H66" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
@@ -2996,18 +2999,18 @@
         <v>1</v>
       </c>
       <c r="C67" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" s="22" t="s">
         <v>38</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>37</v>
       </c>
       <c r="F67" s="22"/>
       <c r="G67" s="22"/>
       <c r="H67" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
@@ -3021,18 +3024,18 @@
         <v>1</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F68" s="22"/>
       <c r="G68" s="22"/>
       <c r="H68" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
@@ -3046,18 +3049,18 @@
         <v>1</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
       <c r="H69" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
@@ -3071,18 +3074,18 @@
         <v>1</v>
       </c>
       <c r="C70" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70" s="22" t="s">
         <v>43</v>
-      </c>
-      <c r="D70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="22" t="s">
-        <v>42</v>
       </c>
       <c r="F70" s="22"/>
       <c r="G70" s="22"/>
       <c r="H70" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
@@ -3096,18 +3099,18 @@
         <v>1</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F71" s="22"/>
       <c r="G71" s="22"/>
       <c r="H71" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
@@ -3121,18 +3124,18 @@
         <v>1</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F72" s="22"/>
       <c r="G72" s="22"/>
       <c r="H72" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
@@ -3149,17 +3152,17 @@
         <v>1</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
@@ -3176,17 +3179,17 @@
         <v>2</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F74" s="22"/>
       <c r="G74" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
@@ -3203,17 +3206,17 @@
         <v>3</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F75" s="22"/>
       <c r="G75" s="22" t="s">
         <v>27</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
@@ -3230,15 +3233,15 @@
         <v>4</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F76" s="22"/>
       <c r="G76" s="22"/>
       <c r="H76" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
@@ -3255,15 +3258,15 @@
         <v>5</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F77" s="22"/>
       <c r="G77" s="22"/>
       <c r="H77" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
@@ -3280,15 +3283,15 @@
         <v>6</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F78" s="22"/>
       <c r="G78" s="22"/>
       <c r="H78" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
@@ -3305,15 +3308,15 @@
         <v>7</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F79" s="22"/>
       <c r="G79" s="22"/>
       <c r="H79" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
@@ -3330,15 +3333,15 @@
         <v>8</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F80" s="22"/>
       <c r="G80" s="22"/>
       <c r="H80" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
@@ -3354,15 +3357,15 @@
         <v>9</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F81" s="22"/>
       <c r="G81" s="22"/>
       <c r="H81" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
@@ -3378,15 +3381,15 @@
         <v>10</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F82" s="22"/>
       <c r="G82" s="22"/>
       <c r="H82" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I82" s="19"/>
       <c r="J82" s="19"/>
@@ -3399,18 +3402,18 @@
         <v>2</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F83" s="22"/>
       <c r="G83" s="22"/>
       <c r="H83" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I83" s="19"/>
     </row>
@@ -3422,18 +3425,18 @@
         <v>2</v>
       </c>
       <c r="C84" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E84" s="22" t="s">
         <v>32</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E84" s="22" t="s">
-        <v>31</v>
       </c>
       <c r="F84" s="22"/>
       <c r="G84" s="22"/>
       <c r="H84" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I84" s="19"/>
     </row>
@@ -3445,18 +3448,18 @@
         <v>2</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F85" s="22"/>
       <c r="G85" s="22"/>
       <c r="H85" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I85" s="19"/>
     </row>
@@ -3468,18 +3471,18 @@
         <v>2</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F86" s="22"/>
       <c r="G86" s="22"/>
       <c r="H86" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I86" s="19"/>
     </row>
@@ -3491,18 +3494,18 @@
         <v>2</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D87" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F87" s="22"/>
       <c r="G87" s="22"/>
       <c r="H87" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I87" s="19"/>
     </row>
@@ -3514,18 +3517,18 @@
         <v>2</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F88" s="22"/>
       <c r="G88" s="22"/>
       <c r="H88" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I88" s="19"/>
     </row>
@@ -3540,17 +3543,17 @@
         <v>1</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F89" s="22"/>
       <c r="G89" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I89" s="19"/>
     </row>
@@ -3565,17 +3568,17 @@
         <v>2</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F90" s="22"/>
       <c r="G90" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3589,17 +3592,17 @@
         <v>3</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F91" s="22"/>
       <c r="G91" s="22" t="s">
         <v>27</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3613,15 +3616,15 @@
         <v>4</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F92" s="22"/>
       <c r="G92" s="22"/>
       <c r="H92" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3635,15 +3638,15 @@
         <v>5</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F93" s="22"/>
       <c r="G93" s="22"/>
       <c r="H93" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3657,15 +3660,15 @@
         <v>6</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F94" s="22"/>
       <c r="G94" s="22"/>
       <c r="H94" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3679,15 +3682,15 @@
         <v>7</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F95" s="22"/>
       <c r="G95" s="22"/>
       <c r="H95" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3701,15 +3704,15 @@
         <v>8</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F96" s="22"/>
       <c r="G96" s="22"/>
       <c r="H96" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3723,15 +3726,15 @@
         <v>9</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F97" s="22"/>
       <c r="G97" s="22"/>
       <c r="H97" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3745,15 +3748,15 @@
         <v>10</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F98" s="22"/>
       <c r="G98" s="22"/>
       <c r="H98" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/PointsAwardRanking.xlsx
+++ b/poker/resources/sample/PointsAwardRanking.xlsx
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="65">
   <si>
     <t>序列ID</t>
   </si>
@@ -266,10 +266,94 @@
     <t>time</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>phone8S</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1990000_4000000</t>
+  </si>
+  <si>
+    <t>1990000_3000000</t>
+  </si>
+  <si>
+    <t>1990000_2000000</t>
+  </si>
+  <si>
+    <t>1990000_1000000</t>
+  </si>
+  <si>
+    <t>1990000_500000</t>
+  </si>
+  <si>
+    <t>11_15</t>
+  </si>
+  <si>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>16_20</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>21_25</t>
+  </si>
+  <si>
+    <t>26_30</t>
+  </si>
+  <si>
+    <t>31_40</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>41_50</t>
+  </si>
+  <si>
+    <t>51_100</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>101_150</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>151_200</t>
+  </si>
+  <si>
+    <t>201_250</t>
+  </si>
+  <si>
+    <t>251_300</t>
+  </si>
+  <si>
+    <t>1990000_5000000</t>
+  </si>
+  <si>
+    <t>1990000_800000</t>
+  </si>
+  <si>
+    <t>1990000_70000000</t>
+  </si>
+  <si>
+    <t>1990000_60000000</t>
+  </si>
+  <si>
+    <t>1990000_50000000</t>
+  </si>
+  <si>
+    <t>1990000_45000000</t>
+  </si>
+  <si>
+    <t>1990000_15000000</t>
+  </si>
+  <si>
+    <t>1990000_27000000</t>
   </si>
   <si>
     <t>%s/test001.jpg</t>
@@ -278,7 +362,10 @@
     <t>%s/web_test001.jpg</t>
   </si>
   <si>
-    <t>phone8S-1</t>
+    <t>2036/08/01 00:00:00</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
   </si>
   <si>
     <t>%s/test002.jpg</t>
@@ -287,97 +374,10 @@
     <t>%s/web_test002.jpg</t>
   </si>
   <si>
-    <t>phone8S-2</t>
-  </si>
-  <si>
     <t>%s/test003.jpg</t>
   </si>
   <si>
     <t>%s/web_test003.jpg</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>11_15</t>
-  </si>
-  <si>
-    <t>1990000_200000</t>
-  </si>
-  <si>
-    <t>16_20</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
-  </si>
-  <si>
-    <t>21_25</t>
-  </si>
-  <si>
-    <t>26_30</t>
-  </si>
-  <si>
-    <t>31_40</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>41_50</t>
-  </si>
-  <si>
-    <t>51_100</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>101_150</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>151_200</t>
-  </si>
-  <si>
-    <t>201_250</t>
-  </si>
-  <si>
-    <t>251_300</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_800000</t>
-  </si>
-  <si>
-    <t>1990000_45000000</t>
-  </si>
-  <si>
-    <t>1990000_15000000</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>1990000_27000000</t>
-  </si>
-  <si>
-    <t>2036/08/01 00:00:00</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
   </si>
   <si>
     <t>1990000_32000000</t>
@@ -588,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1594,12 +1594,8 @@
         <v>23</v>
       </c>
       <c r="F5" s="13"/>
-      <c r="G5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="15"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -1618,15 +1614,11 @@
         <v>22</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" s="13"/>
-      <c r="G6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>28</v>
-      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
       <c r="I6" s="15"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -1645,15 +1637,11 @@
         <v>22</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F7" s="13"/>
-      <c r="G7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
       <c r="I7" s="15"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -1669,10 +1657,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
@@ -1692,10 +1680,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
@@ -1715,10 +1703,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -1738,10 +1726,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
@@ -1761,10 +1749,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
@@ -1784,10 +1772,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1806,10 +1794,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
@@ -1825,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
@@ -1849,13 +1837,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
@@ -1872,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
@@ -1895,13 +1883,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -1918,13 +1906,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -1941,13 +1929,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
@@ -1964,13 +1952,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
@@ -1987,13 +1975,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
@@ -2010,13 +1998,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
@@ -2033,13 +2021,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
@@ -2056,13 +2044,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
@@ -2085,15 +2073,11 @@
         <v>22</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F26" s="13"/>
-      <c r="G26" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
       <c r="I26" s="15"/>
       <c r="K26" s="16"/>
       <c r="M26" s="1"/>
@@ -2112,15 +2096,11 @@
         <v>22</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F27" s="13"/>
-      <c r="G27" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>28</v>
-      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
       <c r="I27" s="15"/>
       <c r="K27" s="16"/>
       <c r="M27" s="1"/>
@@ -2139,15 +2119,11 @@
         <v>22</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F28" s="13"/>
-      <c r="G28" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
       <c r="I28" s="15"/>
       <c r="M28" s="1"/>
     </row>
@@ -2162,10 +2138,10 @@
         <v>4</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
@@ -2183,10 +2159,10 @@
         <v>5</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
@@ -2205,10 +2181,10 @@
         <v>6</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
@@ -2227,10 +2203,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
@@ -2249,10 +2225,10 @@
         <v>8</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
@@ -2271,10 +2247,10 @@
         <v>9</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
@@ -2292,10 +2268,10 @@
         <v>10</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
@@ -2310,13 +2286,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
@@ -2331,13 +2307,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
@@ -2352,13 +2328,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
@@ -2373,13 +2349,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
@@ -2394,13 +2370,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -2415,13 +2391,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
@@ -2442,15 +2418,11 @@
         <v>22</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F42" s="13"/>
-      <c r="G42" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
       <c r="I42" s="15"/>
     </row>
     <row r="43" spans="1:11">
@@ -2467,15 +2439,11 @@
         <v>22</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F43" s="13"/>
-      <c r="G43" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>28</v>
-      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
       <c r="I43" s="15"/>
     </row>
     <row r="44" spans="1:11">
@@ -2492,15 +2460,11 @@
         <v>22</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F44" s="13"/>
-      <c r="G44" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
       <c r="I44" s="15"/>
     </row>
     <row r="45" spans="1:11">
@@ -2514,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
@@ -2535,10 +2499,10 @@
         <v>5</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
@@ -2556,10 +2520,10 @@
         <v>6</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
@@ -2577,10 +2541,10 @@
         <v>7</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
@@ -2598,10 +2562,10 @@
         <v>8</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
@@ -2621,10 +2585,10 @@
         <v>9</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F50" s="13"/>
       <c r="G50" s="13"/>
@@ -2644,10 +2608,10 @@
         <v>10</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
@@ -2667,20 +2631,20 @@
         <v>1</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F52" s="18"/>
       <c r="G52" s="18" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
@@ -2696,20 +2660,20 @@
         <v>2</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F53" s="18"/>
       <c r="G53" s="18" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I53" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
@@ -2725,20 +2689,20 @@
         <v>3</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F54" s="18"/>
       <c r="G54" s="18" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
@@ -2754,16 +2718,16 @@
         <v>4</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F55" s="18"/>
       <c r="G55" s="18"/>
       <c r="H55" s="18"/>
       <c r="I55" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
@@ -2779,16 +2743,16 @@
         <v>5</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F56" s="18"/>
       <c r="G56" s="18"/>
       <c r="H56" s="18"/>
       <c r="I56" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K56" s="16"/>
       <c r="M56" s="1"/>
@@ -2804,16 +2768,16 @@
         <v>6</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F57" s="18"/>
       <c r="G57" s="18"/>
       <c r="H57" s="18"/>
       <c r="I57" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K57" s="16"/>
       <c r="M57" s="1"/>
@@ -2829,16 +2793,16 @@
         <v>7</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F58" s="18"/>
       <c r="G58" s="18"/>
       <c r="H58" s="18"/>
       <c r="I58" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K58" s="16"/>
       <c r="M58" s="1"/>
@@ -2854,16 +2818,16 @@
         <v>8</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F59" s="18"/>
       <c r="G59" s="18"/>
       <c r="H59" s="18"/>
       <c r="I59" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K59" s="16"/>
       <c r="M59" s="1"/>
@@ -2879,16 +2843,16 @@
         <v>9</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F60" s="18"/>
       <c r="G60" s="18"/>
       <c r="H60" s="18"/>
       <c r="I60" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M60" s="1"/>
     </row>
@@ -2903,16 +2867,16 @@
         <v>10</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F61" s="18"/>
       <c r="G61" s="18"/>
       <c r="H61" s="18"/>
       <c r="I61" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M61" s="1"/>
     </row>
@@ -2924,19 +2888,19 @@
         <v>1</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F62" s="18"/>
       <c r="G62" s="18"/>
       <c r="H62" s="18"/>
       <c r="I62" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
@@ -2950,19 +2914,19 @@
         <v>1</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F63" s="18"/>
       <c r="G63" s="18"/>
       <c r="H63" s="18"/>
       <c r="I63" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K63" s="16"/>
       <c r="M63" s="1"/>
@@ -2975,19 +2939,19 @@
         <v>1</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F64" s="18"/>
       <c r="G64" s="18"/>
       <c r="H64" s="18"/>
       <c r="I64" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K64" s="16"/>
       <c r="M64" s="1"/>
@@ -3000,19 +2964,19 @@
         <v>1</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F65" s="18"/>
       <c r="G65" s="18"/>
       <c r="H65" s="18"/>
       <c r="I65" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K65" s="16"/>
       <c r="M65" s="1"/>
@@ -3025,19 +2989,19 @@
         <v>1</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F66" s="18"/>
       <c r="G66" s="18"/>
       <c r="H66" s="18"/>
       <c r="I66" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K66" s="16"/>
       <c r="M66" s="1"/>
@@ -3050,19 +3014,19 @@
         <v>1</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F67" s="18"/>
       <c r="G67" s="18"/>
       <c r="H67" s="18"/>
       <c r="I67" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K67" s="16"/>
       <c r="M67" s="1"/>
@@ -3075,19 +3039,19 @@
         <v>1</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F68" s="18"/>
       <c r="G68" s="18"/>
       <c r="H68" s="18"/>
       <c r="I68" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K68" s="16"/>
       <c r="M68" s="1"/>
@@ -3100,19 +3064,19 @@
         <v>1</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F69" s="18"/>
       <c r="G69" s="18"/>
       <c r="H69" s="18"/>
       <c r="I69" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K69" s="16"/>
       <c r="M69" s="1"/>
@@ -3125,19 +3089,19 @@
         <v>1</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F70" s="18"/>
       <c r="G70" s="18"/>
       <c r="H70" s="18"/>
       <c r="I70" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K70" s="16"/>
       <c r="M70" s="1"/>
@@ -3150,19 +3114,19 @@
         <v>1</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F71" s="18"/>
       <c r="G71" s="18"/>
       <c r="H71" s="18"/>
       <c r="I71" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K71" s="16"/>
       <c r="M71" s="1"/>
@@ -3175,19 +3139,19 @@
         <v>1</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F72" s="18"/>
       <c r="G72" s="18"/>
       <c r="H72" s="18"/>
       <c r="I72" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K72" s="16"/>
       <c r="M72" s="1"/>
@@ -3203,20 +3167,20 @@
         <v>1</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E73" s="18" t="s">
         <v>60</v>
       </c>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="I73" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K73" s="16"/>
       <c r="M73" s="1"/>
@@ -3232,20 +3196,20 @@
         <v>2</v>
       </c>
       <c r="D74" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E74" s="18" t="s">
         <v>61</v>
       </c>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K74" s="16"/>
       <c r="M74" s="1"/>
@@ -3261,20 +3225,20 @@
         <v>3</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="I75" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K75" s="16"/>
       <c r="M75" s="1"/>
@@ -3290,16 +3254,16 @@
         <v>4</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F76" s="18"/>
       <c r="G76" s="18"/>
       <c r="H76" s="18"/>
       <c r="I76" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K76" s="16"/>
       <c r="M76" s="1"/>
@@ -3315,16 +3279,16 @@
         <v>5</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F77" s="18"/>
       <c r="G77" s="18"/>
       <c r="H77" s="18"/>
       <c r="I77" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K77" s="16"/>
       <c r="M77" s="1"/>
@@ -3340,16 +3304,16 @@
         <v>6</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="18"/>
       <c r="H78" s="18"/>
       <c r="I78" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K78" s="16"/>
       <c r="M78" s="1"/>
@@ -3365,16 +3329,16 @@
         <v>7</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F79" s="18"/>
       <c r="G79" s="18"/>
       <c r="H79" s="18"/>
       <c r="I79" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K79" s="16"/>
       <c r="M79" s="1"/>
@@ -3390,16 +3354,16 @@
         <v>8</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F80" s="18"/>
       <c r="G80" s="18"/>
       <c r="H80" s="18"/>
       <c r="I80" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K80" s="16"/>
     </row>
@@ -3414,16 +3378,16 @@
         <v>9</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F81" s="18"/>
       <c r="G81" s="18"/>
       <c r="H81" s="18"/>
       <c r="I81" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K81" s="16"/>
     </row>
@@ -3438,16 +3402,16 @@
         <v>10</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="18"/>
       <c r="H82" s="18"/>
       <c r="I82" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3458,19 +3422,19 @@
         <v>2</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F83" s="18"/>
       <c r="G83" s="18"/>
       <c r="H83" s="18"/>
       <c r="I83" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3481,19 +3445,19 @@
         <v>2</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D84" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F84" s="18"/>
       <c r="G84" s="18"/>
       <c r="H84" s="18"/>
       <c r="I84" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3504,19 +3468,19 @@
         <v>2</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="18"/>
       <c r="H85" s="18"/>
       <c r="I85" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3527,19 +3491,19 @@
         <v>2</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D86" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F86" s="18"/>
       <c r="G86" s="18"/>
       <c r="H86" s="18"/>
       <c r="I86" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3550,19 +3514,19 @@
         <v>2</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F87" s="18"/>
       <c r="G87" s="18"/>
       <c r="H87" s="18"/>
       <c r="I87" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3573,19 +3537,19 @@
         <v>2</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D88" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F88" s="18"/>
       <c r="G88" s="18"/>
       <c r="H88" s="18"/>
       <c r="I88" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3599,20 +3563,20 @@
         <v>1</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F89" s="18"/>
       <c r="G89" s="18" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="I89" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3626,20 +3590,20 @@
         <v>2</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E90" s="22" t="s">
         <v>63</v>
       </c>
       <c r="F90" s="18"/>
       <c r="G90" s="18" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I90" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3653,20 +3617,20 @@
         <v>3</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E91" s="22" t="s">
         <v>64</v>
       </c>
       <c r="F91" s="18"/>
       <c r="G91" s="18" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="I91" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3680,16 +3644,16 @@
         <v>4</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E92" s="22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F92" s="18"/>
       <c r="G92" s="18"/>
       <c r="H92" s="18"/>
       <c r="I92" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -3703,16 +3667,16 @@
         <v>5</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E93" s="22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F93" s="18"/>
       <c r="G93" s="18"/>
       <c r="H93" s="18"/>
       <c r="I93" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -3726,16 +3690,16 @@
         <v>6</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E94" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F94" s="18"/>
       <c r="G94" s="18"/>
       <c r="H94" s="18"/>
       <c r="I94" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -3749,16 +3713,16 @@
         <v>7</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E95" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F95" s="18"/>
       <c r="G95" s="18"/>
       <c r="H95" s="18"/>
       <c r="I95" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -3772,16 +3736,16 @@
         <v>8</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E96" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F96" s="18"/>
       <c r="G96" s="18"/>
       <c r="H96" s="18"/>
       <c r="I96" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3795,16 +3759,16 @@
         <v>9</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F97" s="18"/>
       <c r="G97" s="18"/>
       <c r="H97" s="18"/>
       <c r="I97" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3818,16 +3782,16 @@
         <v>10</v>
       </c>
       <c r="D98" s="24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E98" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F98" s="18"/>
       <c r="G98" s="18"/>
       <c r="H98" s="18"/>
       <c r="I98" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
